--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-susceptibility.xlsx
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Assessment ValueSet for phenotypic susceptibility testing: the categories susceptible, intermediate, susceptible at increased exposure, resistant and non-susceptible.</t>
+    <t>Assessment ValueSet for phenotypic susceptibility testing: the categories susceptible, intermediate, susceptible, increased exposure, resistant and non-susceptible.</t>
   </si>
   <si>
     <t>Purpose</t>
